--- a/artfynd/A 29561-2025 artfynd.xlsx
+++ b/artfynd/A 29561-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>105164169</v>
+        <v>105164165</v>
       </c>
       <c r="B2" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>607649.0781004571</v>
+        <v>607573</v>
       </c>
       <c r="R2" t="n">
-        <v>7040002.099724013</v>
+        <v>7039838</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,14 @@
           <t>2022-10-09</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-10-09</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Riklig</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,16 +784,11 @@
         <v>105164166</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -831,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>607623.214953342</v>
+        <v>607623</v>
       </c>
       <c r="R3" t="n">
-        <v>7039918.909039679</v>
+        <v>7039919</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -864,19 +849,9 @@
           <t>2022-10-09</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-10-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,37 +882,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111602046</v>
+        <v>111601956</v>
       </c>
       <c r="B4" t="n">
-        <v>78605</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -947,10 +917,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>607764.8518122645</v>
+        <v>607674</v>
       </c>
       <c r="R4" t="n">
-        <v>7040115.614522786</v>
+        <v>7040105</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,19 +950,9 @@
           <t>2023-08-20</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-08-20</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,15 +979,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111601956</v>
+        <v>111601952</v>
       </c>
       <c r="B5" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1035,21 +990,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1059,10 +1014,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>607673.8436191129</v>
+        <v>607822</v>
       </c>
       <c r="R5" t="n">
-        <v>7040104.48802998</v>
+        <v>7039926</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1092,19 +1047,9 @@
           <t>2023-08-20</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-08-20</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,15 +1076,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111601952</v>
+        <v>111601957</v>
       </c>
       <c r="B6" t="n">
-        <v>77267</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1171,10 +1111,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>607822.3118785822</v>
+        <v>607633</v>
       </c>
       <c r="R6" t="n">
-        <v>7039926.528511801</v>
+        <v>7040051</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1204,19 +1144,9 @@
           <t>2023-08-20</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-08-20</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1243,15 +1173,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111601957</v>
+        <v>105164169</v>
       </c>
       <c r="B7" t="n">
-        <v>77267</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1259,37 +1184,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Tannflohöjden, Ång</t>
+          <t>Norrtannflo värdetrakt, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>607632.6527975923</v>
+        <v>607649</v>
       </c>
       <c r="R7" t="n">
-        <v>7040050.756075719</v>
+        <v>7040002</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1313,22 +1238,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-08-20</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-10-09</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1343,15 +1258,504 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
+          <t>Jennifer C. Johansson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Amanda Tas, Erland Lindblad, Steve Daurer</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Naturvärdesinventering Y-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>111601938</v>
+      </c>
+      <c r="B8" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Tannflohöjden, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>607692</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7039760</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-08-20</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-08-20</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
           <t>Anders Malmsten</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>Anders Malmsten</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>111601936</v>
+      </c>
+      <c r="B9" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Tannflohöjden, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>607692</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7039760</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-08-20</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-08-20</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>111601939</v>
+      </c>
+      <c r="B10" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Tannflohöjden, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>607738</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7039736</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-08-20</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-08-20</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>111602046</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Tannflohöjden, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>607765</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7040115</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-08-20</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-08-20</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>111601935</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Tannflohöjden, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>607692</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7039760</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-08-20</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-08-20</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29561-2025 artfynd.xlsx
+++ b/artfynd/A 29561-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105164165</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105164166</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -976,6 +991,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111601956</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1073,6 +1093,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111601952</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1170,6 +1195,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111601957</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1271,6 +1301,11 @@
           <t>Naturvärdesinventering Y-län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105164169</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1368,6 +1403,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111601938</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1465,6 +1505,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111601936</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1562,6 +1607,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111601939</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1659,6 +1709,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111602046</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1756,8 +1811,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111601935</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>